--- a/artfynd/A 40017-2026 artfynd.xlsx
+++ b/artfynd/A 40017-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759752</v>
       </c>
       <c r="B2" t="n">
-        <v>92113</v>
+        <v>92115</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40017-2026 artfynd.xlsx
+++ b/artfynd/A 40017-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759752</v>
       </c>
       <c r="B2" t="n">
-        <v>92115</v>
+        <v>92117</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40017-2026 artfynd.xlsx
+++ b/artfynd/A 40017-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759752</v>
       </c>
       <c r="B2" t="n">
-        <v>92117</v>
+        <v>92118</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40017-2026 artfynd.xlsx
+++ b/artfynd/A 40017-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759752</v>
       </c>
       <c r="B2" t="n">
-        <v>92118</v>
+        <v>92124</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40017-2026 artfynd.xlsx
+++ b/artfynd/A 40017-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759752</v>
       </c>
       <c r="B2" t="n">
-        <v>92124</v>
+        <v>92128</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40017-2026 artfynd.xlsx
+++ b/artfynd/A 40017-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759752</v>
       </c>
       <c r="B2" t="n">
-        <v>92128</v>
+        <v>92130</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40017-2026 artfynd.xlsx
+++ b/artfynd/A 40017-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759752</v>
       </c>
       <c r="B2" t="n">
-        <v>92130</v>
+        <v>92143</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40017-2026 artfynd.xlsx
+++ b/artfynd/A 40017-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759752</v>
       </c>
       <c r="B2" t="n">
-        <v>92143</v>
+        <v>92145</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40017-2026 artfynd.xlsx
+++ b/artfynd/A 40017-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759752</v>
       </c>
       <c r="B2" t="n">
-        <v>92145</v>
+        <v>92148</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40017-2026 artfynd.xlsx
+++ b/artfynd/A 40017-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759752</v>
       </c>
       <c r="B2" t="n">
-        <v>92148</v>
+        <v>92158</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>

--- a/artfynd/A 40017-2026 artfynd.xlsx
+++ b/artfynd/A 40017-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136759752</v>
       </c>
       <c r="B2" t="n">
-        <v>92158</v>
+        <v>92159</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
